--- a/PERFIL_NAMPULA_CICLO_4.xlsx
+++ b/PERFIL_NAMPULA_CICLO_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/Pam_Verde/2026/Pam_Ciclo_4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_9DF2353E2D0A4EB38E73D63D5600CBDEECE17C74" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E25CD30B-5CDA-4CB0-9C68-DE1B4528CAE3}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_9DF2353E2D0A4EB38E73D63D5600CBDEECE17C74" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7CBBAFF-2C37-41D2-94E4-D332D21D5B07}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PAM_VERDE_BASELINE_ENDLINE_Repo!$A$1:$CG$51</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4440" uniqueCount="1236">
   <si>
     <t>Confirma que compreendeu a informação acima e aceita participar nesta entrevista?</t>
   </si>
@@ -3900,6 +3900,149 @@
   <si>
     <t>Activa</t>
   </si>
+  <si>
+    <t>Neusa Domingos</t>
+  </si>
+  <si>
+    <t>IVANDRA CHALES</t>
+  </si>
+  <si>
+    <t>MUHIVIRE</t>
+  </si>
+  <si>
+    <t>IVAS MIMIMOS</t>
+  </si>
+  <si>
+    <t>FOI NO DIA 28 NO MES PASSADO FIZ MAQUIAGEM E PETEADO  PARA 5 NOIVAS A FACILIDADE QUE EU TIVE HE QUE ESTAVAO NO MESMO LOCAL E NAO TIVE QUE ME DESLOCAR PARA IR ATENDER UMA DECA VEZ E ISSO ME BENIFICIOU MUITO</t>
+  </si>
+  <si>
+    <t>Loja ou banca própria (física),Venda em casa (clientes que vêm a casa),Mercado ou feira,Entrega ao domicílio (delivery),WhatsApp / WhatsApp Business,Facebook,Outro website ou plataforma online</t>
+  </si>
+  <si>
+    <t>CRESCER NA VIZIBILIDADE DO MEU NEGOCIO</t>
+  </si>
+  <si>
+    <t>ELE ESTA PASSAR POR DIFICULDADE PORQUE NAO TEM APOIO NO LAR, NAO TEM LIBERDADE, NA MINHA OPINIAO ELA TEM QUE CONVERSAR COM O MARIDO SOBRE O NEGOCIO</t>
+  </si>
+  <si>
+    <t>AFECTA SIM POR NAO HAVER LIBERDADE</t>
+  </si>
+  <si>
+    <t>CONVERSAR COM OMARIDO DIALOGAR SOBRE O NEGOCIO</t>
+  </si>
+  <si>
+    <t>SIM ACONTECE  CONVERSADO COM ELE E TER UMA SOLUCAO</t>
+  </si>
+  <si>
+    <t>A  EMPREENDEDORA RECONHECE A RELACAO DO PODER MAIS ELA NAO DA MUITOS DETALHES EM OUTRAS QUESTOES</t>
+  </si>
+  <si>
+    <t>R=10000
+V=4000 &gt;  3000-2500
+O=2500     = 500</t>
+  </si>
+  <si>
+    <t>P=20+20+20+20=80
+MP=80×150=12000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPRO MAIS MATERIAS </t>
+  </si>
+  <si>
+    <t>FACO ANOTACAO POR DIA E POR SEMANA DO TRABALHO QUE FACO</t>
+  </si>
+  <si>
+    <t>PRIMEIRO CADA ERRO TEM QUE PEDIR DESCULPA E CORRIGIR  ESSE ERRO SE ACLIENTE NAO GOSTOU DAS TRACAS DISMACHO PARA FAZER DE NOVO PORQUE JA ESTIVE NESSA SITUACAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEMPRE QUE EU FACO UM SERVICO NO FINAL PERGUNTO SE ELE GOSTOU OU NAO E POR EXEMPLO SE ESTOU A LAVAR CABELO SE UM CLIENTE PERGUNTA SE O CABELO NAO LHE DA COMIXAO E ANTES DE SAIR DO LAVATORIO PERGUNTO NOVAMENTE SE ELA DIZ SIM VOLTA NOVAMENTE NO LAVATORIO ISSO VARIA DE CADA CLIENTE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TENTO PROCURAR COMO FAZER ESSE SERVICO  PROCURO ME INFORMAR OU PESQUISAR NA INTERNET </t>
+  </si>
+  <si>
+    <t>NO EXERCICIO 2 A EMPREENDEDORA ESTA MAIS ABERTA NAS RESPOSTAS,  COMENTA MAIS ATE DA EXEMPLO</t>
+  </si>
+  <si>
+    <t>A EMPREENDEDORA NAO QUESTIONOU, TENTOU NEGOCIAR PARA LEVA A MERCADORIA DEPOIS PAGAR O REMANESCENTE, VISTO QUE O FORNECEDOR RECUSOU A PROPOSTA ELA DISSE QUE VAI REDUZIR A QUANTIDADE DA MERCADORIA</t>
+  </si>
+  <si>
+    <t>O EXERCICIO 3 ELA ESTEVE ABERTA E ENTROU NA PERSONAGEM DO CLIENTE</t>
+  </si>
+  <si>
+    <t>PAM_2026_C4_57</t>
+  </si>
+  <si>
+    <t>MARAVILHA JANUARIO  CARIA</t>
+  </si>
+  <si>
+    <t>DOCES MARAVILHA</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>TIVE UMA NEGOCIACAO, COM UMA EMPRESA QUE QUERIA UMA QUANTIDADE DOS MEUS PRODUTOS, E NEGOCIAMOS ELES ME PAGARAM O VALOR QUE EU QUERIA. SO QUE A DIFERENCA FOI NA MODALIDADE DA NEGOCIACAO, EU ELES DERAM 30% DO VALOR QUE EU QUERIA NAQUELE INSTANTE PARA FAZER O PRODUTO! O RESTO ELES DERAM DEPOIS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TROCANDO AS EMBALAGENS DE PLASTICO PARA EMBALAGEM DE PAPEL, PORQUE AS EMBALAGENS DE PAPEL SAO FACEIS DE SE DECOMPOR, E AS EMBALAGENS DE PLASTICO SAO DIFÍCEIS DE SE DECOMPOR E FICA MAIS TEMPO NO SOLO. </t>
+  </si>
+  <si>
+    <t>EXPECTATIVA, APRENDER OU SABER COMO ACELERAR O MEU NEGOCIO. ADQUIRIR OUTRAS FERRAMENTAS DE MODO A AJUDAR A IMPULSIONAR O MEU NEGOCIO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA MINHA OPINIAO EH QUE A JOANA TEM UM MARIDO MACHISTA, EGOÍSTA DE ALGUMA FORMA ELA DEVE ESTAR A SOFRER UMA VIOLENCIA BASEADA NO   GENERO. A MINHA OPINIAO E QUE A JOANA NAO DEIXE DE IR A FEIRA, E ELA DEVE CONVERSAR COM O MARIDO PARA PODER LHE FAZER PERCEBER DO QUAO IMPORTANTE ELA DEVE IR A FEIRA </t>
+  </si>
+  <si>
+    <t>SIM AFECTA. UMA VES QUE ELA NAO VAI A FEIRA, NAO VAI CONSEGUIR CRESCER COM O NEGOCIO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCURAR AJUDA DE PESSOAS QUE POSSAM ACONSELHAR O MARIDO. E DE CERTA FORMA ELA NAO PODE PARAR </t>
+  </si>
+  <si>
+    <t>A EMPREENDEDORA SUGERIU UMA ESTRATEGIA DE RESPOSTA PARA A JOANA</t>
+  </si>
+  <si>
+    <t>10.000-4000-2500=3500</t>
+  </si>
+  <si>
+    <t>150×80=6000
+6000+6000=12.000</t>
+  </si>
+  <si>
+    <t>ORGANIZAR STOCK, TER MATERIAL SUFICIENTE PARA RESPONDER A ESSA PROCURA.</t>
+  </si>
+  <si>
+    <t>ANOTANDO TODAS ENTRADAS E SAIDAS, PARA SABER COMO AS VENDAS ESTAO INDO.</t>
+  </si>
+  <si>
+    <t>PEDIRIA DESCULPA, SE TIVESSE UM TERMO QUE AMBAS AS PARTES NAO SAIAM PREJUDICADOS RETIFICARIA.</t>
+  </si>
+  <si>
+    <t>ATRAVES DELES MESMO, DEPOIS QUE RECEBEM  O PRODUTO. PERGUNTAR O QUE ACHARAM E SE GOSTARAM</t>
+  </si>
+  <si>
+    <t>INFORMARIA O CLIENTE QUE NAO SEI FAZER, E DEPOIS PROCURAR APRENDER.</t>
+  </si>
+  <si>
+    <t>A EMPREENDEDORA MOSTRA HABILIDADES EM TODAS NEGOCIACOES</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PORQUE AUMENTOU! VISTO QUE EU NAO FUI AVISADA ANTES, PECO QUE ME FACA UM DESCONTO DE 20% VOU PAGAR UMA QUANTIDADE MAIOR.
+ESTA BEM VOU PROCURAR OUTROS FORNECEDORES </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A EMPREENDEDORA NAO FICOU FELIZ COM A INFORMACAO. E REFERIU A POSSIBILIDADE DE PROCURAR NOVOS FORNECEDORES.</t>
+  </si>
+  <si>
+    <t>PAM_2026_C4_58</t>
+  </si>
+  <si>
+    <t>PAM_2026_C4_59</t>
+  </si>
+  <si>
+    <t>MINDOCA NARCISO MAHLAULE</t>
+  </si>
 </sst>
 </file>
 
@@ -3908,10 +4051,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4275,7 +4424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CH51"/>
+  <dimension ref="A1:CU54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
@@ -16774,7 +16923,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="49" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -17034,7 +17183,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="50" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>85</v>
       </c>
@@ -17294,7 +17443,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="51" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>85</v>
       </c>
@@ -17551,6 +17700,648 @@
         <v>103</v>
       </c>
       <c r="CH51" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="52" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46154</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D52" t="s">
+        <v>87</v>
+      </c>
+      <c r="E52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H52" t="s">
+        <v>91</v>
+      </c>
+      <c r="I52" s="1">
+        <v>39119</v>
+      </c>
+      <c r="J52" t="s">
+        <v>92</v>
+      </c>
+      <c r="K52" t="s">
+        <v>93</v>
+      </c>
+      <c r="L52" t="s">
+        <v>94</v>
+      </c>
+      <c r="M52" t="s">
+        <v>1192</v>
+      </c>
+      <c r="N52" t="s">
+        <v>1193</v>
+      </c>
+      <c r="O52" t="s">
+        <v>275</v>
+      </c>
+      <c r="P52" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>99</v>
+      </c>
+      <c r="R52" t="s">
+        <v>400</v>
+      </c>
+      <c r="S52" t="s">
+        <v>101</v>
+      </c>
+      <c r="T52" s="2">
+        <v>10</v>
+      </c>
+      <c r="U52" t="s">
+        <v>102</v>
+      </c>
+      <c r="V52" t="s">
+        <v>103</v>
+      </c>
+      <c r="W52" t="s">
+        <v>103</v>
+      </c>
+      <c r="X52" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF52" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG52" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>1195</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>148</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>112</v>
+      </c>
+      <c r="AM52" t="s">
+        <v>112</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO52" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AQ52" t="s">
+        <v>149</v>
+      </c>
+      <c r="AR52" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS52" t="s">
+        <v>103</v>
+      </c>
+      <c r="AT52" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU52" t="s">
+        <v>1196</v>
+      </c>
+      <c r="AV52" t="s">
+        <v>118</v>
+      </c>
+      <c r="AW52" t="s">
+        <v>1197</v>
+      </c>
+      <c r="AX52" t="s">
+        <v>1198</v>
+      </c>
+      <c r="AY52" t="s">
+        <v>1199</v>
+      </c>
+      <c r="AZ52" t="s">
+        <v>1200</v>
+      </c>
+      <c r="BA52" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB52" t="s">
+        <v>180</v>
+      </c>
+      <c r="BC52" t="s">
+        <v>180</v>
+      </c>
+      <c r="BD52" t="s">
+        <v>112</v>
+      </c>
+      <c r="BE52" t="s">
+        <v>180</v>
+      </c>
+      <c r="BF52" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG52" t="s">
+        <v>1201</v>
+      </c>
+      <c r="BH52" t="s">
+        <v>1202</v>
+      </c>
+      <c r="BI52" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ52" t="s">
+        <v>1203</v>
+      </c>
+      <c r="BK52" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL52" t="s">
+        <v>1204</v>
+      </c>
+      <c r="BM52" t="s">
+        <v>190</v>
+      </c>
+      <c r="BN52" t="s">
+        <v>1205</v>
+      </c>
+      <c r="BO52" t="s">
+        <v>190</v>
+      </c>
+      <c r="BP52" t="s">
+        <v>1206</v>
+      </c>
+      <c r="BQ52" t="s">
+        <v>125</v>
+      </c>
+      <c r="BR52" t="s">
+        <v>1207</v>
+      </c>
+      <c r="BS52" t="s">
+        <v>125</v>
+      </c>
+      <c r="BT52" t="s">
+        <v>1208</v>
+      </c>
+      <c r="BU52" t="s">
+        <v>125</v>
+      </c>
+      <c r="BV52" t="s">
+        <v>132</v>
+      </c>
+      <c r="BW52" t="s">
+        <v>133</v>
+      </c>
+      <c r="BX52" t="s">
+        <v>134</v>
+      </c>
+      <c r="BY52" t="s">
+        <v>1209</v>
+      </c>
+      <c r="BZ52" t="s">
+        <v>1210</v>
+      </c>
+      <c r="CA52" t="s">
+        <v>99</v>
+      </c>
+      <c r="CB52" t="s">
+        <v>112</v>
+      </c>
+      <c r="CC52" t="s">
+        <v>99</v>
+      </c>
+      <c r="CD52" t="s">
+        <v>99</v>
+      </c>
+      <c r="CE52" t="s">
+        <v>112</v>
+      </c>
+      <c r="CF52" t="s">
+        <v>164</v>
+      </c>
+      <c r="CG52" t="s">
+        <v>1211</v>
+      </c>
+      <c r="CH52" t="s">
+        <v>1189</v>
+      </c>
+      <c r="CI52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CJ52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CK52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CN52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CQ52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CR52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CS52" t="s">
+        <v>103</v>
+      </c>
+      <c r="CT52" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CU52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46162</v>
+      </c>
+      <c r="C53" t="s">
+        <v>165</v>
+      </c>
+      <c r="D53" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H53" t="s">
+        <v>91</v>
+      </c>
+      <c r="I53" s="1">
+        <v>36216</v>
+      </c>
+      <c r="J53" t="s">
+        <v>92</v>
+      </c>
+      <c r="K53" t="s">
+        <v>93</v>
+      </c>
+      <c r="L53" t="s">
+        <v>197</v>
+      </c>
+      <c r="M53" t="s">
+        <v>103</v>
+      </c>
+      <c r="N53" t="s">
+        <v>1214</v>
+      </c>
+      <c r="O53" t="s">
+        <v>1215</v>
+      </c>
+      <c r="P53" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>99</v>
+      </c>
+      <c r="R53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S53" t="s">
+        <v>170</v>
+      </c>
+      <c r="T53" s="2">
+        <v>10</v>
+      </c>
+      <c r="U53" t="s">
+        <v>102</v>
+      </c>
+      <c r="V53" t="s">
+        <v>103</v>
+      </c>
+      <c r="W53" t="s">
+        <v>103</v>
+      </c>
+      <c r="X53" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF53" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG53" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>148</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>112</v>
+      </c>
+      <c r="AM53" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO53" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP53" t="s">
+        <v>229</v>
+      </c>
+      <c r="AQ53" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR53" t="s">
+        <v>1217</v>
+      </c>
+      <c r="AS53" t="s">
+        <v>116</v>
+      </c>
+      <c r="AT53" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU53" t="s">
+        <v>1218</v>
+      </c>
+      <c r="AV53" t="s">
+        <v>176</v>
+      </c>
+      <c r="AW53" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AX53" t="s">
+        <v>1220</v>
+      </c>
+      <c r="AY53" t="s">
+        <v>1221</v>
+      </c>
+      <c r="AZ53" t="s">
+        <v>176</v>
+      </c>
+      <c r="BA53" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB53" t="s">
+        <v>112</v>
+      </c>
+      <c r="BC53" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD53" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE53" t="s">
+        <v>99</v>
+      </c>
+      <c r="BF53" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG53" t="s">
+        <v>1222</v>
+      </c>
+      <c r="BH53" t="s">
+        <v>1223</v>
+      </c>
+      <c r="BI53" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ53" t="s">
+        <v>1224</v>
+      </c>
+      <c r="BK53" t="s">
+        <v>190</v>
+      </c>
+      <c r="BL53" t="s">
+        <v>1225</v>
+      </c>
+      <c r="BM53" t="s">
+        <v>125</v>
+      </c>
+      <c r="BN53" t="s">
+        <v>1226</v>
+      </c>
+      <c r="BO53" t="s">
+        <v>125</v>
+      </c>
+      <c r="BP53" t="s">
+        <v>1227</v>
+      </c>
+      <c r="BQ53" t="s">
+        <v>125</v>
+      </c>
+      <c r="BR53" t="s">
+        <v>1228</v>
+      </c>
+      <c r="BS53" t="s">
+        <v>125</v>
+      </c>
+      <c r="BT53" t="s">
+        <v>1229</v>
+      </c>
+      <c r="BU53" t="s">
+        <v>125</v>
+      </c>
+      <c r="BV53" t="s">
+        <v>132</v>
+      </c>
+      <c r="BW53" t="s">
+        <v>133</v>
+      </c>
+      <c r="BX53" t="s">
+        <v>134</v>
+      </c>
+      <c r="BY53" t="s">
+        <v>1230</v>
+      </c>
+      <c r="BZ53" t="s">
+        <v>1231</v>
+      </c>
+      <c r="CA53" t="s">
+        <v>112</v>
+      </c>
+      <c r="CB53" t="s">
+        <v>112</v>
+      </c>
+      <c r="CC53" t="s">
+        <v>112</v>
+      </c>
+      <c r="CD53" t="s">
+        <v>112</v>
+      </c>
+      <c r="CE53" t="s">
+        <v>99</v>
+      </c>
+      <c r="CF53" t="s">
+        <v>137</v>
+      </c>
+      <c r="CG53" t="s">
+        <v>1232</v>
+      </c>
+      <c r="CH53" t="s">
+        <v>1189</v>
+      </c>
+      <c r="CI53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CJ53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CK53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CL53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CM53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CN53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CO53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CP53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CQ53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CR53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CS53" t="s">
+        <v>103</v>
+      </c>
+      <c r="CT53" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CU53" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D54" t="s">
+        <v>87</v>
+      </c>
+      <c r="E54" t="s">
+        <v>88</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H54" t="s">
+        <v>91</v>
+      </c>
+      <c r="I54" s="1">
+        <v>34387</v>
+      </c>
+      <c r="J54" t="s">
+        <v>92</v>
+      </c>
+      <c r="K54" t="s">
+        <v>93</v>
+      </c>
+      <c r="L54" t="s">
+        <v>197</v>
+      </c>
+      <c r="P54" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>112</v>
+      </c>
+      <c r="CH54" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -17559,11 +18350,23 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CH51">
     <sortCondition ref="F1:F51"/>
   </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -17572,7 +18375,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -17807,30 +18610,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AE6AA50-BA9D-4FE9-8F77-FF1D3A337A62}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F8B143F-BF2A-4757-BC4D-A353A36DAAA9}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5481EECA-E144-4148-B5F0-6CF69713C758}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -17839,4 +18619,31 @@
     <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AE6AA50-BA9D-4FE9-8F77-FF1D3A337A62}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F8B143F-BF2A-4757-BC4D-A353A36DAAA9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>